--- a/artfynd/A 6836-2026 artfynd.xlsx
+++ b/artfynd/A 6836-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97102174</v>
+        <v>97102149</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>424</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721392.5268518154</v>
+        <v>721410</v>
       </c>
       <c r="R2" t="n">
-        <v>6392370.583613308</v>
+        <v>6392438</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +784,7 @@
         <v>97102172</v>
       </c>
       <c r="B3" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721392.5268518154</v>
+        <v>721393</v>
       </c>
       <c r="R3" t="n">
-        <v>6392370.583613308</v>
+        <v>6392370</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +849,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Börje H Fagerlind, Sten Svantesson</t>
+          <t>Sten Svantesson, Börje H Fagerlind</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -917,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97102176</v>
+        <v>97102170</v>
       </c>
       <c r="B4" t="n">
-        <v>88845</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4188</v>
+        <v>3767</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721392.5268518154</v>
+        <v>721399</v>
       </c>
       <c r="R4" t="n">
-        <v>6392370.583613308</v>
+        <v>6392411</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,26 +955,21 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1027,7 +987,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Börje H Fagerlind, Sten Svantesson</t>
+          <t>Sten Svantesson, Börje H Fagerlind</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1038,15 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97102173</v>
+        <v>97102176</v>
       </c>
       <c r="B5" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91322</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>4188</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721392.5268518154</v>
+        <v>721393</v>
       </c>
       <c r="R5" t="n">
-        <v>6392370.583613308</v>
+        <v>6392370</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,19 +1066,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,6 +1097,647 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>97102158</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1250 m V om Mästermyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>721421</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6392391</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Äldre kalkbarrsog, talldominerad</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>97102173</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>1250 m V om Mästermyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>721393</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6392370</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre kalkbarrsog, talldominerad</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>97102174</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1250 m V om Mästermyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>721393</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6392370</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre kalkbarrsog, talldominerad</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131261614</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mästermyr, 1250 m V om, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>721393</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6392371</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>I-Got-3682</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre kalkbarrsog, talldominerad</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>97102157</v>
+      </c>
+      <c r="B10" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1250 m V om Mästermyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>721421</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6392391</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre kalkbarrsog, talldominerad</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>97102171</v>
+      </c>
+      <c r="B11" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1250 m V om Mästermyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>721399</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6392411</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre kalkbarrsog, talldominerad</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>

--- a/artfynd/A 6836-2026 artfynd.xlsx
+++ b/artfynd/A 6836-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97102149</v>
+        <v>135169564</v>
       </c>
       <c r="B2" t="n">
-        <v>87193</v>
+        <v>100424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>424</v>
+        <v>174</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1250 m V om Mästermyr, Gtl</t>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721410</v>
+        <v>721214</v>
       </c>
       <c r="R2" t="n">
-        <v>6392438</v>
+        <v>6392274</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,32 +768,28 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre kalkbarrsog, talldominerad</t>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Börje H Fagerlind</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Börje H Fagerlind, Sten Svantesson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97102172</v>
+        <v>135169572</v>
       </c>
       <c r="B3" t="n">
-        <v>91680</v>
+        <v>100424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,37 +797,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>174</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1250 m V om Mästermyr, Gtl</t>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721393</v>
+        <v>721287</v>
       </c>
       <c r="R3" t="n">
-        <v>6392370</v>
+        <v>6392386</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -846,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -865,70 +879,75 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Äldre kalkbarrsog, talldominerad</t>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Börje H Fagerlind</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Börje H Fagerlind</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97102170</v>
+        <v>135169593</v>
       </c>
       <c r="B4" t="n">
-        <v>87391</v>
+        <v>100424</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3767</v>
+        <v>174</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1250 m V om Mästermyr, Gtl</t>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721399</v>
+        <v>721351</v>
       </c>
       <c r="R4" t="n">
-        <v>6392411</v>
+        <v>6392436</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -952,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,42 +985,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Äldre kalkbarrsog, talldominerad</t>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Börje H Fagerlind</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Börje H Fagerlind</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97102176</v>
+        <v>135169623</v>
       </c>
       <c r="B5" t="n">
-        <v>91322</v>
+        <v>100424</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,37 +1019,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4188</v>
+        <v>174</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1250 m V om Mästermyr, Gtl</t>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721393</v>
+        <v>721207</v>
       </c>
       <c r="R5" t="n">
-        <v>6392370</v>
+        <v>6392306</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,12 +1073,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,70 +1092,75 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre kalkbarrsog, talldominerad</t>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Börje H Fagerlind</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Börje H Fagerlind, Sten Svantesson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97102158</v>
+        <v>135169627</v>
       </c>
       <c r="B6" t="n">
-        <v>93209</v>
+        <v>100424</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>174</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1250 m V om Mästermyr, Gtl</t>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721421</v>
+        <v>721203</v>
       </c>
       <c r="R6" t="n">
-        <v>6392391</v>
+        <v>6392300</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1169,12 +1184,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,32 +1203,28 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre kalkbarrsog, talldominerad</t>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Börje H Fagerlind</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Börje H Fagerlind</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97102173</v>
+        <v>135169628</v>
       </c>
       <c r="B7" t="n">
-        <v>92869</v>
+        <v>100424</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,37 +1232,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>174</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1250 m V om Mästermyr, Gtl</t>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721393</v>
+        <v>721190</v>
       </c>
       <c r="R7" t="n">
-        <v>6392370</v>
+        <v>6392288</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,12 +1295,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,70 +1314,75 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre kalkbarrsog, talldominerad</t>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Börje H Fagerlind</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Börje H Fagerlind</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97102174</v>
+        <v>135169630</v>
       </c>
       <c r="B8" t="n">
-        <v>99118</v>
+        <v>100424</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>174</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1250 m V om Mästermyr, Gtl</t>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721393</v>
+        <v>721183</v>
       </c>
       <c r="R8" t="n">
-        <v>6392370</v>
+        <v>6392274</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1381,12 +1406,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,70 +1425,75 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre kalkbarrsog, talldominerad</t>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Börje H Fagerlind</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Börje H Fagerlind</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131261614</v>
+        <v>135169632</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>100424</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>174</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mästermyr, 1250 m V om, Gtl</t>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>721393</v>
+        <v>721197</v>
       </c>
       <c r="R9" t="n">
-        <v>6392371</v>
+        <v>6392278</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1485,19 +1515,14 @@
           <t>Vallstena</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>I-Got-3682</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,70 +1536,75 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre kalkbarrsog, talldominerad</t>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Börje H Fagerlind</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97102157</v>
+        <v>135169634</v>
       </c>
       <c r="B10" t="n">
-        <v>87346</v>
+        <v>100424</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003295</v>
+        <v>174</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1250 m V om Mästermyr, Gtl</t>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721421</v>
+        <v>721202</v>
       </c>
       <c r="R10" t="n">
-        <v>6392391</v>
+        <v>6392278</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,12 +1628,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1617,70 +1647,75 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre kalkbarrsog, talldominerad</t>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Börje H Fagerlind</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Börje H Fagerlind</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97102171</v>
+        <v>135169647</v>
       </c>
       <c r="B11" t="n">
-        <v>87346</v>
+        <v>100424</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>174</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1250 m V om Mästermyr, Gtl</t>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721399</v>
+        <v>721220</v>
       </c>
       <c r="R11" t="n">
-        <v>6392411</v>
+        <v>6392235</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1704,12 +1739,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1723,21 +1758,6427 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre kalkbarrsog, talldominerad</t>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>97102149</v>
+      </c>
+      <c r="B12" t="n">
+        <v>87193</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>424</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1250 m V om Mästermyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>721410</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6392438</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre kalkbarrsog, talldominerad</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Börje H Fagerlind</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Börje H Fagerlind, Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135169571</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100743</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>783</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>721287</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6392386</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135169609</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100743</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>783</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>721184</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6392379</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135169613</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100743</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>783</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>721183</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6392372</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135169645</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100743</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>783</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>721206</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6392239</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>97102172</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91680</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1250 m V om Mästermyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>721393</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6392370</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Äldre kalkbarrsog, talldominerad</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Sten Svantesson, Börje H Fagerlind</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>97102170</v>
+      </c>
+      <c r="B18" t="n">
+        <v>87391</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3767</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Violettfläckig spindling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1250 m V om Mästermyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>721399</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6392411</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre kalkbarrsog, talldominerad</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>97102176</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91322</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>1250 m V om Mästermyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>721393</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6392370</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Äldre kalkbarrsog, talldominerad</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Börje H Fagerlind, Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>97102158</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1250 m V om Mästermyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>721421</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6392391</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Äldre kalkbarrsog, talldominerad</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>97102173</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>1250 m V om Mästermyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>721393</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6392370</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Äldre kalkbarrsog, talldominerad</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135169701</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>721224</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6392288</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Tall högstubbe, kraftigt bearbetad av spillkråka (äldre och färska).</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135169702</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>721270</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6392363</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Död tall, stående med gott om insektshål. Spillkråka födosök (äldre).</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135169703</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>721377</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6392386</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gran, låga med gott om insektshål. Födosök av spillkråka i nedre delen.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135169704</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>721368</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6392429</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gran död, stående med myuror vid basen, där födosök spillkråka (färskt)</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135169705</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>721346</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6392444</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre död tall på sockel. Gott om insektshål. Spillkråka födosök (äldre).</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135169706</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>721277</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6392404</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Död tall, stående med gott om insektshål. Spillkråka födosök (färska).</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135169707</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>721226</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6392344</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Död tall, lutande med gott om insektshål. Spillkråka födosök (äldre).</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135169709</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>721207</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6392306</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Död, stående gran, spillkråka födosök vid rot (aldre).</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135169710</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>721208</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6392278</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Död, stående tall med gott om insektshå; födosök av spillkråka.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135169711</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>721221</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6392267</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Tallåga, grov med insektshål.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135169708</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58698</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>721170</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6392429</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135169569</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99087</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>219769</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cephalanthera longifolia</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>721270</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6392363</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135169590</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99087</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219769</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cephalanthera longifolia</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>721359</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6392433</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135169606</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99173</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>721184</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6392379</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135169648</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99173</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>721220</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6392230</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135169587</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99233</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>721368</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6392429</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135169597</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99233</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>721330</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6392446</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Sumpskog mot N och O.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135169608</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99233</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>721184</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6392379</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135169567</v>
+      </c>
+      <c r="B40" t="n">
+        <v>108197</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>721261</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6392356</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135169570</v>
+      </c>
+      <c r="B41" t="n">
+        <v>108197</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>721270</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6392363</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135169574</v>
+      </c>
+      <c r="B42" t="n">
+        <v>108197</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>721308</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6392369</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135169575</v>
+      </c>
+      <c r="B43" t="n">
+        <v>108197</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>721331</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6392369</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135169576</v>
+      </c>
+      <c r="B44" t="n">
+        <v>108197</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>721347</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6392372</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135169577</v>
+      </c>
+      <c r="B45" t="n">
+        <v>108197</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>721357</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6392380</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135169617</v>
+      </c>
+      <c r="B46" t="n">
+        <v>108197</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>721226</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6392336</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135169618</v>
+      </c>
+      <c r="B47" t="n">
+        <v>108197</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>721227</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6392269</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135169626</v>
+      </c>
+      <c r="B48" t="n">
+        <v>108197</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>721207</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6392306</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135169635</v>
+      </c>
+      <c r="B49" t="n">
+        <v>108197</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>721202</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6392278</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135169637</v>
+      </c>
+      <c r="B50" t="n">
+        <v>108197</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>721207</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6392272</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135169639</v>
+      </c>
+      <c r="B51" t="n">
+        <v>108197</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>721221</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6392267</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135169640</v>
+      </c>
+      <c r="B52" t="n">
+        <v>108197</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>721216</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6392254</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135169641</v>
+      </c>
+      <c r="B53" t="n">
+        <v>108197</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>721201</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6392257</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135169650</v>
+      </c>
+      <c r="B54" t="n">
+        <v>108197</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>721220</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6392230</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135169653</v>
+      </c>
+      <c r="B55" t="n">
+        <v>108197</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>721218</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6392223</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135169655</v>
+      </c>
+      <c r="B56" t="n">
+        <v>108197</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>721241</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6392165</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Torräng.</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135169589</v>
+      </c>
+      <c r="B57" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>721359</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6392433</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135169562</v>
+      </c>
+      <c r="B58" t="n">
+        <v>106894</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>721243</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6392246</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Grovt och högt dött träd.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135169584</v>
+      </c>
+      <c r="B59" t="n">
+        <v>106894</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>721384</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6392431</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135169592</v>
+      </c>
+      <c r="B60" t="n">
+        <v>106894</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>721351</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6392436</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135169602</v>
+      </c>
+      <c r="B61" t="n">
+        <v>106894</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>721325</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6392435</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre träd samt sly.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135169607</v>
+      </c>
+      <c r="B62" t="n">
+        <v>106894</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>721184</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6392379</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135169643</v>
+      </c>
+      <c r="B63" t="n">
+        <v>106894</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>721201</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6392251</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Röjd 5 cm i diameter. Skott finns.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135169652</v>
+      </c>
+      <c r="B64" t="n">
+        <v>106894</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>721212</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6392223</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>97102174</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>1250 m V om Mästermyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>721393</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6392370</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Äldre kalkbarrsog, talldominerad</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>131261614</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Mästermyr, 1250 m V om, Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>721393</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6392371</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>I-Got-3682</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Äldre kalkbarrsog, talldominerad</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135169595</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99113</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Vallstena Slumre 1:19 (5) A 6836-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>721346</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6392444</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd inför avverkning.</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>97102157</v>
+      </c>
+      <c r="B68" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>1250 m V om Mästermyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>721421</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6392391</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Äldre kalkbarrsog, talldominerad</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskogar på Gotland 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>97102171</v>
+      </c>
+      <c r="B69" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>1250 m V om Mästermyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>721399</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6392411</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Vallstena</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Äldre kalkbarrsog, talldominerad</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>

--- a/artfynd/A 6836-2026 artfynd.xlsx
+++ b/artfynd/A 6836-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169564</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169572</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169593</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169623</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169627</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169628</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169630</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1551,6 +1591,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169632</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,6 +1707,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169634</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1773,6 +1823,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169647</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1879,6 +1934,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97102149</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1990,6 +2050,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169571</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2101,6 +2166,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169609</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2212,6 +2282,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169613</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2323,6 +2398,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169645</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2429,6 +2509,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97102172</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2540,6 +2625,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97102170</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2646,6 +2736,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97102176</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2752,6 +2847,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97102158</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2858,6 +2958,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97102173</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2970,6 +3075,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169701</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3082,6 +3192,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169702</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3194,6 +3309,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169703</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3306,6 +3426,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169704</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3418,6 +3543,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169705</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3530,6 +3660,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169706</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3642,6 +3777,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169707</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3754,6 +3894,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169709</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3866,6 +4011,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169710</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3978,6 +4128,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169711</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4089,6 +4244,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169708</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4200,6 +4360,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169569</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4311,6 +4476,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169590</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4422,6 +4592,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169606</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4533,6 +4708,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169648</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4644,6 +4824,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169587</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4760,6 +4945,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169597</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4871,6 +5061,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169608</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4982,6 +5177,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169567</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5093,6 +5293,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169570</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5204,6 +5409,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169574</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5315,6 +5525,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169575</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5426,6 +5641,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169576</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5537,6 +5757,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169577</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5648,6 +5873,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169617</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5759,6 +5989,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169618</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5870,6 +6105,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169626</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5981,6 +6221,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169635</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6092,6 +6337,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169637</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6203,6 +6453,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169639</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6314,6 +6569,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169640</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6425,6 +6685,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169641</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6536,6 +6801,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169650</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6647,6 +6917,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169653</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6758,6 +7033,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169655</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6869,6 +7149,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169589</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6985,6 +7270,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169562</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7096,6 +7386,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169584</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7198,6 +7493,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169592</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7314,6 +7614,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169602</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7425,6 +7730,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169607</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7541,6 +7851,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169643</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7643,6 +7958,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169652</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7749,6 +8069,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97102174</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7860,6 +8185,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131261614</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7971,6 +8301,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135169595</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8077,6 +8412,11 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97102157</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8183,8 +8523,83 @@
           <t>Inventering av kalkbarrskogar på Gotland 2021</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97102171</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 6836-2026 artfynd.xlsx
+++ b/artfynd/A 6836-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135169564</v>
       </c>
       <c r="B2" t="n">
-        <v>100424</v>
+        <v>100471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135169572</v>
       </c>
       <c r="B3" t="n">
-        <v>100424</v>
+        <v>100471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135169593</v>
       </c>
       <c r="B4" t="n">
-        <v>100424</v>
+        <v>100471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135169623</v>
       </c>
       <c r="B5" t="n">
-        <v>100424</v>
+        <v>100471</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>135169627</v>
       </c>
       <c r="B6" t="n">
-        <v>100424</v>
+        <v>100471</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>135169628</v>
       </c>
       <c r="B7" t="n">
-        <v>100424</v>
+        <v>100471</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>135169630</v>
       </c>
       <c r="B8" t="n">
-        <v>100424</v>
+        <v>100471</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>135169632</v>
       </c>
       <c r="B9" t="n">
-        <v>100424</v>
+        <v>100471</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>135169634</v>
       </c>
       <c r="B10" t="n">
-        <v>100424</v>
+        <v>100471</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>135169647</v>
       </c>
       <c r="B11" t="n">
-        <v>100424</v>
+        <v>100471</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>135169571</v>
       </c>
       <c r="B13" t="n">
-        <v>100743</v>
+        <v>100791</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>135169609</v>
       </c>
       <c r="B14" t="n">
-        <v>100743</v>
+        <v>100791</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>135169613</v>
       </c>
       <c r="B15" t="n">
-        <v>100743</v>
+        <v>100791</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>135169645</v>
       </c>
       <c r="B16" t="n">
-        <v>100743</v>
+        <v>100791</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>135169701</v>
       </c>
       <c r="B22" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>135169702</v>
       </c>
       <c r="B23" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>135169703</v>
       </c>
       <c r="B24" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>135169704</v>
       </c>
       <c r="B25" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>135169705</v>
       </c>
       <c r="B26" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>135169706</v>
       </c>
       <c r="B27" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>135169707</v>
       </c>
       <c r="B28" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>135169709</v>
       </c>
       <c r="B29" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>135169710</v>
       </c>
       <c r="B30" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>135169711</v>
       </c>
       <c r="B31" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>135169708</v>
       </c>
       <c r="B32" t="n">
-        <v>58698</v>
+        <v>58703</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>135169569</v>
       </c>
       <c r="B33" t="n">
-        <v>99087</v>
+        <v>99134</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>135169590</v>
       </c>
       <c r="B34" t="n">
-        <v>99087</v>
+        <v>99134</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>135169606</v>
       </c>
       <c r="B35" t="n">
-        <v>99173</v>
+        <v>99220</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>135169648</v>
       </c>
       <c r="B36" t="n">
-        <v>99173</v>
+        <v>99220</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>135169587</v>
       </c>
       <c r="B37" t="n">
-        <v>99233</v>
+        <v>99280</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>135169597</v>
       </c>
       <c r="B38" t="n">
-        <v>99233</v>
+        <v>99280</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>135169608</v>
       </c>
       <c r="B39" t="n">
-        <v>99233</v>
+        <v>99280</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>135169567</v>
       </c>
       <c r="B40" t="n">
-        <v>108197</v>
+        <v>108252</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>135169570</v>
       </c>
       <c r="B41" t="n">
-        <v>108197</v>
+        <v>108252</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>135169574</v>
       </c>
       <c r="B42" t="n">
-        <v>108197</v>
+        <v>108252</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>135169575</v>
       </c>
       <c r="B43" t="n">
-        <v>108197</v>
+        <v>108252</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>135169576</v>
       </c>
       <c r="B44" t="n">
-        <v>108197</v>
+        <v>108252</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>135169577</v>
       </c>
       <c r="B45" t="n">
-        <v>108197</v>
+        <v>108252</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>135169617</v>
       </c>
       <c r="B46" t="n">
-        <v>108197</v>
+        <v>108252</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>135169618</v>
       </c>
       <c r="B47" t="n">
-        <v>108197</v>
+        <v>108252</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>135169626</v>
       </c>
       <c r="B48" t="n">
-        <v>108197</v>
+        <v>108252</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>135169635</v>
       </c>
       <c r="B49" t="n">
-        <v>108197</v>
+        <v>108252</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>135169637</v>
       </c>
       <c r="B50" t="n">
-        <v>108197</v>
+        <v>108252</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>135169639</v>
       </c>
       <c r="B51" t="n">
-        <v>108197</v>
+        <v>108252</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>135169640</v>
       </c>
       <c r="B52" t="n">
-        <v>108197</v>
+        <v>108252</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>135169641</v>
       </c>
       <c r="B53" t="n">
-        <v>108197</v>
+        <v>108252</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>135169650</v>
       </c>
       <c r="B54" t="n">
-        <v>108197</v>
+        <v>108252</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>135169653</v>
       </c>
       <c r="B55" t="n">
-        <v>108197</v>
+        <v>108252</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>135169655</v>
       </c>
       <c r="B56" t="n">
-        <v>108197</v>
+        <v>108252</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>135169589</v>
       </c>
       <c r="B57" t="n">
-        <v>110159</v>
+        <v>110215</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>135169562</v>
       </c>
       <c r="B58" t="n">
-        <v>106894</v>
+        <v>106949</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>135169584</v>
       </c>
       <c r="B59" t="n">
-        <v>106894</v>
+        <v>106949</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>135169592</v>
       </c>
       <c r="B60" t="n">
-        <v>106894</v>
+        <v>106949</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>135169602</v>
       </c>
       <c r="B61" t="n">
-        <v>106894</v>
+        <v>106949</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>135169607</v>
       </c>
       <c r="B62" t="n">
-        <v>106894</v>
+        <v>106949</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>135169643</v>
       </c>
       <c r="B63" t="n">
-        <v>106894</v>
+        <v>106949</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>135169652</v>
       </c>
       <c r="B64" t="n">
-        <v>106894</v>
+        <v>106949</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>135169595</v>
       </c>
       <c r="B67" t="n">
-        <v>99113</v>
+        <v>99160</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 6836-2026 artfynd.xlsx
+++ b/artfynd/A 6836-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135169564</v>
       </c>
       <c r="B2" t="n">
-        <v>100471</v>
+        <v>100498</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135169572</v>
       </c>
       <c r="B3" t="n">
-        <v>100471</v>
+        <v>100498</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135169593</v>
       </c>
       <c r="B4" t="n">
-        <v>100471</v>
+        <v>100498</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135169623</v>
       </c>
       <c r="B5" t="n">
-        <v>100471</v>
+        <v>100498</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>135169627</v>
       </c>
       <c r="B6" t="n">
-        <v>100471</v>
+        <v>100498</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>135169628</v>
       </c>
       <c r="B7" t="n">
-        <v>100471</v>
+        <v>100498</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>135169630</v>
       </c>
       <c r="B8" t="n">
-        <v>100471</v>
+        <v>100498</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>135169632</v>
       </c>
       <c r="B9" t="n">
-        <v>100471</v>
+        <v>100498</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>135169634</v>
       </c>
       <c r="B10" t="n">
-        <v>100471</v>
+        <v>100498</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>135169647</v>
       </c>
       <c r="B11" t="n">
-        <v>100471</v>
+        <v>100498</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>135169571</v>
       </c>
       <c r="B13" t="n">
-        <v>100791</v>
+        <v>100818</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>135169609</v>
       </c>
       <c r="B14" t="n">
-        <v>100791</v>
+        <v>100818</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>135169613</v>
       </c>
       <c r="B15" t="n">
-        <v>100791</v>
+        <v>100818</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>135169645</v>
       </c>
       <c r="B16" t="n">
-        <v>100791</v>
+        <v>100818</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>135169569</v>
       </c>
       <c r="B33" t="n">
-        <v>99134</v>
+        <v>99161</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>135169590</v>
       </c>
       <c r="B34" t="n">
-        <v>99134</v>
+        <v>99161</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>135169606</v>
       </c>
       <c r="B35" t="n">
-        <v>99220</v>
+        <v>99247</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>135169648</v>
       </c>
       <c r="B36" t="n">
-        <v>99220</v>
+        <v>99247</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>135169587</v>
       </c>
       <c r="B37" t="n">
-        <v>99280</v>
+        <v>99307</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>135169597</v>
       </c>
       <c r="B38" t="n">
-        <v>99280</v>
+        <v>99307</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>135169608</v>
       </c>
       <c r="B39" t="n">
-        <v>99280</v>
+        <v>99307</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>135169567</v>
       </c>
       <c r="B40" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>135169570</v>
       </c>
       <c r="B41" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>135169574</v>
       </c>
       <c r="B42" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>135169575</v>
       </c>
       <c r="B43" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>135169576</v>
       </c>
       <c r="B44" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>135169577</v>
       </c>
       <c r="B45" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>135169617</v>
       </c>
       <c r="B46" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>135169618</v>
       </c>
       <c r="B47" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>135169626</v>
       </c>
       <c r="B48" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>135169635</v>
       </c>
       <c r="B49" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>135169637</v>
       </c>
       <c r="B50" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>135169639</v>
       </c>
       <c r="B51" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>135169640</v>
       </c>
       <c r="B52" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>135169641</v>
       </c>
       <c r="B53" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>135169650</v>
       </c>
       <c r="B54" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>135169653</v>
       </c>
       <c r="B55" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>135169655</v>
       </c>
       <c r="B56" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>135169589</v>
       </c>
       <c r="B57" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>135169562</v>
       </c>
       <c r="B58" t="n">
-        <v>106949</v>
+        <v>106976</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>135169584</v>
       </c>
       <c r="B59" t="n">
-        <v>106949</v>
+        <v>106976</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>135169592</v>
       </c>
       <c r="B60" t="n">
-        <v>106949</v>
+        <v>106976</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>135169602</v>
       </c>
       <c r="B61" t="n">
-        <v>106949</v>
+        <v>106976</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>135169607</v>
       </c>
       <c r="B62" t="n">
-        <v>106949</v>
+        <v>106976</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>135169643</v>
       </c>
       <c r="B63" t="n">
-        <v>106949</v>
+        <v>106976</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>135169652</v>
       </c>
       <c r="B64" t="n">
-        <v>106949</v>
+        <v>106976</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>135169595</v>
       </c>
       <c r="B67" t="n">
-        <v>99160</v>
+        <v>99187</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
